--- a/tests/fixtures/sample.xlsx
+++ b/tests/fixtures/sample.xlsx
@@ -2,84 +2,81 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="個案清單" sheetId="1" r:id="rId1"/>
-    <sheet name="承辦" sheetId="2" r:id="rId2"/>
+    <sheet name="个案清单" sheetId="1" r:id="rId1"/>
+    <sheet name="承办" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve">姓名</t>
   </si>
   <si>
-    <t xml:space="preserve">身分證字號</t>
-  </si>
-  <si>
-    <t xml:space="preserve">手機</t>
+    <t xml:space="preserve">身份证号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手机</t>
   </si>
   <si>
     <t xml:space="preserve">地址</t>
   </si>
   <si>
-    <t xml:space="preserve">備註</t>
+    <t xml:space="preserve">备注</t>
   </si>
   <si>
     <t xml:space="preserve">王小明</t>
   </si>
   <si>
-    <t xml:space="preserve">A123456789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0912-345-678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">台北市信義區市府路45號8樓</t>
+    <t xml:space="preserve">110101199003078515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-1234-5678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">北京市朝阳区建国路88号</t>
   </si>
   <si>
     <t xml:space="preserve">林美玲</t>
   </si>
   <si>
-    <t xml:space="preserve">B223456782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">新北市板橋區文化路一段188巷3號之2</t>
+    <t xml:space="preserve">440305198512250027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">杭州市西湖区文一西路969号</t>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
       </rPr>
-      <t xml:space="preserve">聯絡人：</t>
+      <t xml:space="preserve">联系人：</t>
     </r>
     <r>
       <rPr>
         <b/>
       </rPr>
-      <t xml:space="preserve">歐陽志遠</t>
+      <t xml:space="preserve">欧阳志远</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">0987654321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">臺中市西屯區台灣大道三段99號</t>
+    <t xml:space="preserve">13600001111</t>
   </si>
   <si>
     <t xml:space="preserve">同上</t>
   </si>
   <si>
-    <t xml:space="preserve">承辦社工</t>
-  </si>
-  <si>
-    <t xml:space="preserve">陳大文</t>
-  </si>
-  <si>
-    <t xml:space="preserve">市話</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(02)2712-3456</t>
+    <t xml:space="preserve">承办社工</t>
+  </si>
+  <si>
+    <t xml:space="preserve">陈大文</t>
+  </si>
+  <si>
+    <t xml:space="preserve">固定电话</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(010)88886666</t>
   </si>
 </sst>
 </file>
@@ -177,10 +174,10 @@
         <v>13</v>
       </c>
       <c r="D4" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s" s="1">
         <v>14</v>
-      </c>
-      <c r="E4" t="s" s="1">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -192,18 +189,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>16</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>17</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s" s="1">
         <v>18</v>
-      </c>
-      <c r="B2" t="s" s="1">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
